--- a/paganti.xlsx
+++ b/paganti.xlsx
@@ -1,17 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Documents\genera-ricevute-campus\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CFF97ED-4A19-4675-9AA6-133739C18A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Paganti" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Paganti" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
     </ext>
@@ -20,39 +36,18 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
-  </numFmts>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -65,7 +60,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -73,107 +68,80 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285f4"/>
+        <a:srgbClr val="4285F4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ea4335"/>
+        <a:srgbClr val="EA4335"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="fbbc04"/>
+        <a:srgbClr val="FBBC04"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34a853"/>
+        <a:srgbClr val="34A853"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="ff6d01"/>
+        <a:srgbClr val="FF6D01"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46bdc6"/>
+        <a:srgbClr val="46BDC6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155cc"/>
+        <a:srgbClr val="1155CC"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155cc"/>
+        <a:srgbClr val="1155CC"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -203,7 +171,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -227,7 +195,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -287,97 +255,100 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="33.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="54.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="29.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18.88"/>
+    <col min="1" max="1" width="22.140625" customWidth="1"/>
+    <col min="2" max="2" width="33.28515625" customWidth="1"/>
+    <col min="3" max="3" width="30.5703125" customWidth="1"/>
+    <col min="4" max="4" width="54.140625" customWidth="1"/>
+    <col min="5" max="5" width="29.140625" customWidth="1"/>
+    <col min="7" max="7" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="str">
-        <f aca="false">IFERROR(__xludf.dummyfunction("QUERY(Richieste!A1:U1000, ""SELECT  C, G,H,I,J,K,L WHERE S = 'ACCETTATO' AND U = 'SI' "")"),"Cognome e Nome del Bambino")</f>
+    <row r="1" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="str">
+        <f ca="1">IFERROR(__xludf.dummyfunction("QUERY(Richieste!A1:U1000, ""SELECT  C, G,H,I,J,K,L WHERE S = 'ACCETTATO' AND U = 'SI' "")"),"Cognome e Nome del Bambino")</f>
         <v>Cognome e Nome del Bambino</v>
       </c>
-      <c r="B1" s="2" t="str">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),"Codice Fiscale del Bambino")</f>
+      <c r="B1" s="1" t="str">
+        <f ca="1">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),"Codice Fiscale del Bambino")</f>
         <v>Codice Fiscale del Bambino</v>
       </c>
-      <c r="C1" s="2" t="str">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),"Nominativo Genitore a cui Intestare la Ricevuta")</f>
+      <c r="C1" s="1" t="str">
+        <f ca="1">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),"Nominativo Genitore a cui Intestare la Ricevuta")</f>
         <v>Nominativo Genitore a cui Intestare la Ricevuta</v>
       </c>
-      <c r="D1" s="2" t="str">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),"Codice Fiscale del Genitore a cui Intestare la Ricevuta")</f>
+      <c r="D1" s="1" t="str">
+        <f ca="1">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),"Codice Fiscale del Genitore a cui Intestare la Ricevuta")</f>
         <v>Codice Fiscale del Genitore a cui Intestare la Ricevuta</v>
       </c>
-      <c r="E1" s="2" t="str">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),"Via di Residenza")</f>
+      <c r="E1" s="1" t="str">
+        <f ca="1">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),"Via di Residenza")</f>
         <v>Via di Residenza</v>
       </c>
-      <c r="F1" s="2" t="str">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),"CITTA")</f>
+      <c r="F1" s="1" t="str">
+        <f ca="1">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),"CITTA")</f>
         <v>CITTA</v>
       </c>
-      <c r="G1" s="2" t="str">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),"CAP")</f>
+      <c r="G1" s="1" t="str">
+        <f ca="1">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),"CAP")</f>
         <v>CAP</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="str">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),"Paolucci Valentino ")</f>
-        <v>Paolucci Valentino </v>
-      </c>
-      <c r="B2" s="2" t="str">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),"PLCVNT18C23G478M")</f>
+    <row r="2" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="str">
+        <f ca="1">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),"Paolucci Valentino ")</f>
+        <v xml:space="preserve">Paolucci Valentino </v>
+      </c>
+      <c r="B2" s="1" t="str">
+        <f ca="1">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),"PLCVNT18C23G478M")</f>
         <v>PLCVNT18C23G478M</v>
       </c>
-      <c r="C2" s="2" t="str">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),"Dorilli Giulia")</f>
+      <c r="C2" s="1" t="str">
+        <f ca="1">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),"Dorilli Giulia")</f>
         <v>Dorilli Giulia</v>
       </c>
-      <c r="D2" s="2" t="str">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),"DRLGLI88P68G478M")</f>
+      <c r="D2" s="1" t="str">
+        <f ca="1">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),"DRLGLI88P68G478M")</f>
         <v>DRLGLI88P68G478M</v>
       </c>
-      <c r="E2" s="2" t="str">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),"Via Fonte dei Lavatoi, n. 23")</f>
+      <c r="E2" s="1" t="str">
+        <f ca="1">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),"Via Fonte dei Lavatoi, n. 23")</f>
         <v>Via Fonte dei Lavatoi, n. 23</v>
       </c>
-      <c r="F2" s="2" t="str">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),"Pila (PG)")</f>
+      <c r="F2" s="1" t="str">
+        <f ca="1">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),"Pila (PG)")</f>
         <v>Pila (PG)</v>
       </c>
-      <c r="G2" s="2" t="str">
-        <f aca="false">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),"06132")</f>
+      <c r="G2" s="1" t="str">
+        <f ca="1">IFERROR(__xludf.dummyfunction("""COMPUTED_VALUE"""),"06132")</f>
         <v>06132</v>
       </c>
+    </row>
+    <row r="3" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.74791666666666701" right="0.74791666666666701" top="0.98402777777777795" bottom="0.98402777777777795" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>